--- a/ASTRA Mail Ops Foundations(1).xlsx
+++ b/ASTRA Mail Ops Foundations(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krianoop1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A16C672-B4AA-429B-907A-A42F66CB5126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7841BF-093D-4A25-A196-B0D0BDF3F1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2952593-99C1-4317-8021-AF64E95F2B85}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
   <si>
     <t>Category</t>
   </si>
@@ -262,167 +262,10 @@
     <t>After completing this video, you will be able to describe the basics of antimalware.</t>
   </si>
   <si>
-    <t>CEH v13: Malware Threats</t>
-  </si>
-  <si>
-    <t>Performing proper malware threat detection and mitigation is vital in cybersecurity as it helps enable organizations to protect their systems and data. In this course, learn about malware, advanced persistent threats (APTs), Trojans, viruses, ransomware, and fileless and AI-based malware. Next, explore malware detection techniques, the importance of AI in cybersecurity, and the application of natural language processing (NLP) in AI-powered attacks. Finally, discover how to perform static and dynamic malware analysis using various tools and methodologies and examine famous case studies about previous malware attacks. This course can be used in preparation for the Certified Ethical Hacker (CEH) 312-50 exam.</t>
-  </si>
-  <si>
     <t>Performing Dynamic Malware Analysis</t>
   </si>
   <si>
     <t>Learn how to perform dynamic malware analysis using methods such as process monitoring, scheduled tasks, and port monitoring.</t>
-  </si>
-  <si>
-    <t>Threat intelligence / IOC analysis</t>
-  </si>
-  <si>
-    <t>Threat Intelligence</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to use OCI Threat Intelligence to enhance Cloud Guard's detection capabilities by aggregating threat data.</t>
-  </si>
-  <si>
-    <t>Indicators of Attack</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to identify and analyze indicators of attack (IoA) for early detection of cyber threats.</t>
-  </si>
-  <si>
-    <t>Internal Intelligence Sources</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to describe how to utilize internal intelligence for proactive threat detection and mitigation.</t>
-  </si>
-  <si>
-    <t>Threat Intelligence Platforms (TIPs)</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to describe how to use TIPs to streamline threat intelligence management and response.</t>
-  </si>
-  <si>
-    <t>Incident response</t>
-  </si>
-  <si>
-    <t>Incident Response</t>
-  </si>
-  <si>
-    <t>During this video, you will learn how to distinguish between incident management activities.</t>
-  </si>
-  <si>
-    <t>Remediation and Incident Response</t>
-  </si>
-  <si>
-    <t>Understand Remediation and ncident Response process</t>
-  </si>
-  <si>
-    <t>Incident Response Lifecycle</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to outline the phases of the incident response lifecycle and their importance.</t>
-  </si>
-  <si>
-    <t>Incident Response Analysis</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to identify how to analyze and respond to various security threats.</t>
-  </si>
-  <si>
-    <t>Incident Response Fundamentals</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to outline the purpose and importance of incident response in cybersecurity operations.</t>
-  </si>
-  <si>
-    <t>Incident Response Process</t>
-  </si>
-  <si>
-    <t>Upon completion of this video, you will be able to outline the incident response process, including preparation, detection, analysis, containment, eradication, recovery, and lessons learned.</t>
-  </si>
-  <si>
-    <t>SIEM / threat hunting</t>
-  </si>
-  <si>
-    <t>Perform threat hunting in Microsoft Sentinel</t>
-  </si>
-  <si>
-    <t>Security Information and Event Management (SIEM)</t>
-  </si>
-  <si>
-    <t>In this video, we will introduce SIEM concepts and their role in security monitoring.</t>
-  </si>
-  <si>
-    <t>Incident Response Integration with SIEM Tools</t>
-  </si>
-  <si>
-    <t>In this video, we will describe integration patterns with Splunk, QRadar, and other SIEM platforms.</t>
-  </si>
-  <si>
-    <t>Python + Regex fundamentals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RegEx Lessons from "The Coding Train": Introduction to Regular Expressions - Programming with Text
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RegEx Lessons from "The Coding Train": Regular Expressions: Capturing Groups - Programming with Text
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RegEx Lessons from "The Coding Train": Regular Expressions: Meta-characters - Programming with Text
-</t>
-  </si>
-  <si>
-    <t>Python String Introduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learn how to manipulate strings including how to index, slice, iterate, and concatenate them.
-</t>
-  </si>
-  <si>
-    <t>Performing String Operations</t>
-  </si>
-  <si>
-    <t>Learn how to perform operations with strings.</t>
-  </si>
-  <si>
-    <t>MITRE ATT&amp;CK / detection engineering</t>
-  </si>
-  <si>
-    <t>MITRE ATT&amp;CK Framework for Threat Mapping</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to identify how to map security events to the MITRE ATT&amp;CK framework.</t>
-  </si>
-  <si>
-    <t>Using the MITRE ATT&amp;CK Framework</t>
-  </si>
-  <si>
-    <t>Learn how to use the MITRE Adversarial Tactics, Techniques, and Common Knowledge (ATT&amp;CK) framework to identify adversarial tactics and techniques.</t>
-  </si>
-  <si>
-    <t>Detection Engineering and Continuous Improvement</t>
-  </si>
-  <si>
-    <t>After completing this video, you will be able to use detection engineering principles to systematically build and measure security monitoring maturity.</t>
-  </si>
-  <si>
-    <t>Attack Patterns</t>
-  </si>
-  <si>
-    <t>Through this video, you will be able to recognize attack patterns to mitigate potential threats.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In this video I discuss capturing parentheses and how they are used to create numbered groups that referenced in a find / replace operation. This is the fourth video in a series on Regular Expressions, which is part of the "Programming from A to Z" course at ITP.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This video is part of week 2 of the "Programming from A to Z" course at ITP (http://itp.nyu.edu). In this video I introduce Regular Expressions. What are they and how are they used? I summarize the topics of future videos including meta-characters, capturing parentheses, character classes and JavaScript functions like split(), match(), test(), replace() and exec().
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In this video I discuss meta-characters: what are they and what role do they play in regular expressions? This is the second video in a series on Regular Expressions, which is part of the "Programming from A to Z" course at ITP.
-</t>
   </si>
   <si>
     <t>In this module, you will:
@@ -431,12 +274,143 @@
 List the different types of network devices used in a network.
 Describe network communication principles like TCP/IP, DNS, and ports.</t>
   </si>
+  <si>
+    <t>Getting Started with Python: Introduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This 15-video course lets learners explore the basics of how to use the Python programming language. You will learn to set up with an interactive environment that allows you to develop and run Python scripts on your machine. Begin by installing Anaconda, an open-source distribution of the Python and R programming languages. You will learn to write your first meaningful program in Python, then create a Jupyter notebook, the most popular tool for writing and running Python code. You will learn how to do simple coding by using Python's Jupyter notebooks, and explore different Jupyter functionalities, including built-in functions. Learners will explore how to use a Python variable to store values, and learn to differentiate between variables of different types, and the different ways to assign values to variables. You will examine how variables act as containers, and you will learn how to change values that are inside a container. Finally, you will learn to use integers, floating-point numbers, strings, and to work with Boolean values.
+</t>
+  </si>
+  <si>
+    <t>Complex Data Types in Python: Working with Lists &amp; Tuples in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learn how to work with lists, tuples, and strings in Jupyter notebook in Python in this 14-video course. You will discover similarities and differences between tuples and lists and see how strings are essentially just a list of characters. Begin with an introduction to lists, and then create and initialize lists in Python. You will then access and update list elements; add, remove, sort, and reverse elements from a list; execute built-in functions with lists, and create new lists from existing lists by using slicing operations. Next, examine how to extract specific elements from the original list using step size; perform list functions on strings; invoke functions on the string object; and access substrings with slicing operations. Receive an introduction to tuples, exploring the similarities between lists and tuples, then move on to understanding tuple immutability by specifying differences between lists and tuples. Then an introduction to other complex data types and using dictionaries and sets in Python. The concluding exercise concerns recalling differences and similarities between lists and tuples.
+</t>
+  </si>
+  <si>
+    <t>Complex Data Types in Python: Working with Dictionaries &amp; Sets in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This 9-video course helps learners explore dictionary data type in Python. Dictionaries are associative containers used to store key-value pairs. Given a key, finding the associated value is optimized by Python to be extremely efficient. First, receive an introduction to dictionaries in Jupyter Notebook in Python. You will learn how to create and initialize dictionaries, then learn about nesting complex data types within dictionaries. Continuing with the study of Python dictionaries, you will explore what functions and methods can be invoked on these dictionaries, such as modifying and updating dictionaries using dictionary methods. Next, you will be introduced to sets, another commonly used complex data type that Python supports. You will then create and initialize sets. This leads on to performing set operations such as union, intersection difference, and other set operations. You will also examine nested lists, and work with nested types within other complex data types. In the final tutorial, you will learn how to convert lists to dictionaries and vice versa. The concluding exercise entails recalling features of dictionaries and sets.
+</t>
+  </si>
+  <si>
+    <t>Complex Data Types in Python: Shallow &amp; Deep Copies in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explore copying operations on containers in Python in this 9-vdeo course, which examines the subtle distinction between shallow and deep copies. Changes made to shallow copies affect the original whereas with deep copies they do not. Learners begin by observing Jupyter notebook in Python, where you will be performing shallow and deep copies of Python strings. You will learn how to create shallow copies of lists, and then create deep copies of lists where changes to the copy do not affect the original. Following this, you will begin working with tuples, a process which you will discover is quite simple because tuples are immutable. So you will learn how to create shallow and deep copies of tuples. You will also learn how deep copies of dictionaries work, and perform shallow and deep copies of sets. In the closing exercise, learners are asked to recall how shallow and deep copies work for complex data types.
+</t>
+  </si>
+  <si>
+    <t>Conditional Statements &amp; Loops: If-else Control Structures in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learners will explore implementations of the order of precedence of operators, using if-elif-else statements to evaluate multiple conditions and conversions between various data types in Python, in this 15-video course. Key concepts covered here include how conditions in Python work, and how to evaluate conditions by involving primitive data types using if statements and complex data types using if statements. Next, evaluate multiple conditions for decision making with nested control structures; identify how to use the if-else statement to make decisions involving complex data types such as lists, tuples, and dictionaries; and learn how to convert an integer to a float and a float or an integer to a string, and vice-versa. Learners then observe how to convert primitive data types to complex data types, to convert between various complex data types, and to convert between various complex data types and view base conversions with Python built-in functions; and to solve various programming problems with Python built-in methods. Finally, you will learn to solve various programming problems by using if-elif-else statements and nested if-else statements.
+</t>
+  </si>
+  <si>
+    <t>Conditional Statements &amp; Loops: The Basics of for Loops in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loops are one way to perform the same operations repeatedly in a program. For loops are the control structure to use when the repeated operations are performed on a sequence such as a list or a tuple. In this 9-video course, you will explore different ways to iterate over a sequence using for loops. Key concepts covered in this course include how to use for loops to process elements in a list and characters in a string; and how to code for loops to iterate over values in a tuple and the keys and values in a dictionary. Next, learn the function of associating an else block with a Python for loop; include if-else statements and other for loops within a for loop; how to generate a sequence of consecutive integers with the range function; and how to use the range function to iterate over a large range of values and apply it within nested for loops. Finally, observe how to write for loops in order to iterate over 1-dimensional and 2-dimensional sequences.
+</t>
+  </si>
+  <si>
+    <t>Conditional Statements &amp; Loops: Advanced Operations Using for Loops in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explore how iterating over elements using for loops can be controlled using the break and continue statements in Python. Creating sequences from other sequences using comprehensions is also covered in this 9-video course. Key concepts covered here include how to terminate a for loop when a specific condition is met using the break statement; learning how the break statement affects the code in the else block of a for loop; and observing how to skip an iteration of a for loop when a specific condition is met using the continue statement. Next, learn how to use the continue statement along with the break statement within the same for loop; learn the fact that no action is performed under specific conditions by using the pass statement; and create a list out of the contents of another list using a comprehension. Finally, you will learn about conditions in list comprehensions in order to filter elements used in the source list and to define values in the newly created list.
+</t>
+  </si>
+  <si>
+    <t>Conditional Statements &amp; Loops: While Loops in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While loops are one way to keep repeating a set of actions until a specific condition is met in Python. In this 11-video course, learners explore the use of while loops, considerations when implementing while loops, and use cases for while loops and for loops. Key concepts covered here include implementing a basic while loop and recognizing what conditions cause it to become an infinite loop; learning to use while loops to carry out actions while evaluating expressions based on numerical and string data; and examining while loops whose iterations depend on user input data. Next, learn syntax for defining while loops within a single line; learn to iterate over a list of elements with while loops; and learn to iterate over multiple lists and tuples with while loops. Learn when it is appropriate to use break keyword to stop a while loop, and learn to break out of a while loop and recognize use of the pass keyword within such loops. Finally, learn skip steps in individual iterations of a while loop using the continue statement.
+</t>
+  </si>
+  <si>
+    <t>Functions in Python: Introduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explore how Python facilitates code reuse by using functions in this 17-video course, which shows learners how to define functions, learn passing arguments to functions, and returning values from functions. The functions you will examine change the state of the program, may have side effects, and have observable effects other than their return values. Since functions with side effects are hard to parallelize and use in a distributed environment, you will learn correct ways of returning values from functions. First, you will learn how to invoke functions by using both positional and keyword arguments. You will next work with positional input arguments in custom functions, and learn that these are required arguments, and how to order these arguments to invoke your function. You will next learn to use variable length arguments in defining custom functions. Finally, you will learn how keyword arguments or named arguments are a way to make the intent behind function invocation absolutely explicit, and help prevent bugs in programs that are especially hard to detect.
+</t>
+  </si>
+  <si>
+    <t>Functions in Python: Gaining a Deeper Understanding of Python Functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This 13-video course offers learners an in-depth exploration of Python functions, by focusing on nuances such as argument passing by value and reference, and local and global variables. In this course, you will examine how functions are first-class citizens in Python, as with other data types. You will examine how Python allows functions to be stored in variables, passed into other functions as arguments, and returned from functions as return values. Next, you will learn how to identify and apply differences between parsing arguments by value and reference. Examine how Python treats functions on par with other data types, a key attribute of a program seeking to support the functional programming paradigm; and learn how to work with use and throw functions by using lam das. This course then covers how lightweight functions for one-off use called lambda functions or anonymous functions play an important role in keeping Python code both succinct and readable. Finally, you will learn how to appropriately choose between local and global variables for use in your program.
+</t>
+  </si>
+  <si>
+    <t>Functions in Python: Working with Advanced Features of Python Functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This course explores advanced Python function topics such as recursion, closures, and using generator functions to generate sequences. In 12 videos, you will learn how to use decorators to add functionality to code; examine how recursion can be used to construct code to solve complex problems; and learn to write a terminating condition for a recursive function. Next, you will learn how to use an Iterator to respond to a built-in next () function. Learners will also examine closures, and how as functions they maintain their own lexical environment; and explore how closures are functions that can yield dramatic results in the distributed processing of code, and are widely used in the implementation of distributed processing frameworks. Then you will learn how to use generator functions to generate sequences. You will learn how sequences can iterated upon by other parts of your program. Finally, you will learn that using decorators offers simple ways of invoking higher-order functions.
+</t>
+  </si>
+  <si>
+    <t>Regular Expression for Data Science</t>
+  </si>
+  <si>
+    <t>Track 1: Learn Regular Expressions</t>
+  </si>
+  <si>
+    <t>Track 2: Text Preprocessing</t>
+  </si>
+  <si>
+    <t>Track 3: Language Parsing</t>
+  </si>
+  <si>
+    <t>Track 4: Data Cleaning</t>
+  </si>
+  <si>
+    <t>In this track of the Regular Expression for Data Science Aspire Journey, the focus will be on utilizing Python and pandas library for cleaning, manipulating, and preparing datasets effectively for further analysis.</t>
+  </si>
+  <si>
+    <t>In this track of the Regular Expression for Data Science Aspire Journey, the focus will be on understanding Natural Language Processing (NLP) and effectively utilizing Regular Expressions (Regex) for text parsing and manipulation.</t>
+  </si>
+  <si>
+    <t>In this track of the Regular Expression for Data Science Aspire Journey, the focus will be on vital programming concepts such as tokenization, stemming, lemmatization, stop words removal, and text normalization using NLTK library.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this track of the Regular Expression for Data Science Aspire Journey, the focus will be on understanding the foundational concepts, syntax, and use of regular expressions.
+</t>
+  </si>
+  <si>
+    <t>Regular Expression</t>
+  </si>
+  <si>
+    <t>Introduction to Regular Expressions</t>
+  </si>
+  <si>
+    <t>Understanding of character sets, optional and fixed quantifiers, literals and anchors for matching text
+Ability to use wildcards and ranges to match a variety of characters
+Knowledge of shorthand character classes and the Kleene star and Kleene plus for specifying quantifiers
+Proficiency with alternation and grouping to create complex regular expressions</t>
+  </si>
+  <si>
+    <t>Python Introduction</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Start coding with Python 3. Master the fundamentals of Python programming including printing, variables, operators, and more.
+Skills you'll gain
+Use the print() function to output messages
+Assign integers and strings to variables
+Manipulate variables using arithmetic operators
+Read and troubleshoot errors</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,28 +420,11 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF6A6E75"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF222325"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -484,7 +441,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -507,44 +464,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -880,725 +890,653 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{909D8762-949C-4922-BC1B-C63BF86CB250}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="71.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="93.5546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="71.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.5546875" style="9" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="3">
         <v>3.2638888888888891E-2</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="108" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="4" t="s">
+      <c r="D2" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="3">
         <v>5.6006944444444443E-2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="3">
         <v>1.2731481481481481E-2</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="3">
         <v>1.0810185185185185E-2</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="3">
         <v>7.3032407407407404E-3</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="3">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="3">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="3">
         <v>4.3518518518518515E-3</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="36" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="3">
         <v>5.0347222222222225E-3</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="15" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="3">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="3">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="3">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="3">
         <v>6.0648148148148145E-3</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="3">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="3">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="3">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="3">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="3">
         <v>5.2083333333333336E-2</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="3">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="3">
         <v>2.7777777777777779E-3</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="3">
         <v>4.2592592592592595E-3</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="3">
         <v>1.4583333333333334E-2</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="4" t="s">
+    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="3">
         <v>1.1111111111111112E-2</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="4" t="s">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="3">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="4" t="s">
+    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="3">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="4" t="s">
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="3">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="3">
         <v>4.8842592592592592E-3</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="4" t="s">
+    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="3">
         <v>3.1365740740740742E-3</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="4" t="s">
+    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="3">
         <v>4.5833333333333334E-3</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="4" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="3">
         <v>3.7615740740740739E-3</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="4" t="s">
+      <c r="A32" s="12"/>
+      <c r="B32" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="3">
         <v>2.1296296296296298E-3</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="4" t="s">
+    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="9">
-        <v>4.431712962962963E-2</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="3">
+        <v>3.5532407407407409E-3</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="9">
-        <v>3.5532407407407409E-3</v>
-      </c>
-      <c r="D34" s="5" t="s">
+    <row r="34" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+      <c r="C34" s="3">
+        <v>6.3194444444444442E-2</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="4" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="9">
-        <v>5.7754629629629631E-3</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="C35" s="3">
+        <v>6.8750000000000006E-2</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="4" t="s">
+    <row r="36" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="9">
-        <v>4.5601851851851853E-3</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="C36" s="3">
+        <v>3.7256944444444447E-2</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="4" t="s">
+    <row r="37" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="9">
-        <v>4.6296296296296294E-3</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="3">
+        <v>3.0555555555555555E-2</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="4" t="s">
+    <row r="38" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="9">
-        <v>4.2824074074074075E-3</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="C38" s="3">
+        <v>7.0081018518518515E-2</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+    <row r="39" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="C39" s="3">
+        <v>4.266203703703704E-2</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="9">
-        <v>3.0324074074074073E-3</v>
-      </c>
-      <c r="D39" s="5" t="s">
+    </row>
+    <row r="40" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="16" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="4" t="s">
+      <c r="C40" s="3">
+        <v>4.5138888888888888E-2</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="9">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="D40" s="5" t="s">
+    </row>
+    <row r="41" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="B41" s="16" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="4" t="s">
+      <c r="C41" s="3">
+        <v>5.486111111111111E-2</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="9">
-        <v>4.3055555555555555E-3</v>
-      </c>
-      <c r="D41" s="5" t="s">
+    </row>
+    <row r="42" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="16" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="4" t="s">
+      <c r="C42" s="3">
+        <v>8.5416666666666669E-2</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="9">
-        <v>5.2662037037037035E-3</v>
-      </c>
-      <c r="D42" s="5" t="s">
+    </row>
+    <row r="43" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="16" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="4" t="s">
+      <c r="C43" s="3">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C43" s="9">
-        <v>4.7453703703703703E-3</v>
-      </c>
-      <c r="D43" s="5" t="s">
+    </row>
+    <row r="44" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="16" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="4" t="s">
+      <c r="C44" s="3">
+        <v>5.9722222222222225E-2</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C44" s="9">
-        <v>7.3611111111111108E-3</v>
-      </c>
-      <c r="D44" s="5" t="s">
+    </row>
+    <row r="45" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" s="3">
+        <v>4.5138888888888888E-2</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="B46" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="C46" s="3">
+        <v>3.8194444444444448E-2</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="9">
-        <v>9.3055555555555558E-2</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
-      <c r="B46" s="4" t="s">
+      <c r="C47" s="3">
+        <v>3.8194444444444448E-2</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8"/>
+      <c r="B48" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="9">
-        <v>2.8356481481481483E-3</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="C48" s="3">
+        <v>7.9861111111111105E-2</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8"/>
+      <c r="B49" s="16" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
-      <c r="B47" s="4" t="s">
+      <c r="C49" s="3">
+        <v>7.9861111111111105E-2</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="9">
-        <v>4.2245370370370371E-3</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="48" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="9">
-        <v>8.3333333333333332E-3</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="36" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="4" t="s">
+    </row>
+    <row r="50" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="9">
-        <v>9.7222222222222224E-3</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="36" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="9">
-        <v>1.1111111111111112E-2</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="4" t="s">
+      <c r="C50" s="3">
+        <v>3.8194444444444448E-2</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="9">
-        <v>3.8194444444444448E-2</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="9">
-        <v>6.7939814814814816E-3</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="9">
-        <v>3.7847222222222223E-3</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C54" s="9">
-        <v>5.1504629629629626E-3</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C55" s="9">
-        <v>8.4606481481481477E-3</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C56" s="9">
-        <v>5.1736111111111115E-3</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>120</v>
-      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="A53:A56"/>
+  <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A13:A18"/>
     <mergeCell ref="A20:A27"/>
-    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A34:A44"/>
+    <mergeCell ref="A46:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
